--- a/rules/CORE-000792/positive/01/data/unit-test-coreid-FB0905-positive.xlsx
+++ b/rules/CORE-000792/positive/01/data/unit-test-coreid-FB0905-positive.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="dm.xpt" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ce.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="cm.xpt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="su.xpt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dm.xpt" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ce.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="su.xpt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ag.xpt" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -68,7 +69,7 @@
       <sz val="7"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +104,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -230,6 +237,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -636,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,6 +710,18 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Substance Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ag.xpt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Agents</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1269,7 @@
           <t>2006-04-01</t>
         </is>
       </c>
-      <c r="L5" s="9" t="n"/>
+      <c r="L5" s="6" t="n"/>
       <c r="M5" s="7" t="n">
         <v>701</v>
       </c>
@@ -1357,7 +1383,7 @@
           <t>2006-03-26</t>
         </is>
       </c>
-      <c r="L6" s="13" t="n"/>
+      <c r="L6" s="6" t="n"/>
       <c r="M6" s="11" t="n">
         <v>701</v>
       </c>
@@ -1571,7 +1597,7 @@
           <t>CETERM</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>CEDECOD</t>
         </is>
@@ -1680,7 +1706,7 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>DEATH</t>
         </is>
@@ -1711,7 +1737,7 @@
           <t>Dead</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>DEATH</t>
         </is>
@@ -3841,4 +3867,320 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>AGSEQ</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>AGTRT</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>AGPRESP</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>AGOCCUR</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>AGDOSE</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>AGDOSU</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>AGVAMT</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>AGVAMTU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Study Identifier</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>Unique Subject Identifier</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>Sequence Number</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr">
+        <is>
+          <t>Reported Agent Name</t>
+        </is>
+      </c>
+      <c r="F2" s="26" t="inlineStr">
+        <is>
+          <t>AG Pre-Specified</t>
+        </is>
+      </c>
+      <c r="G2" s="26" t="inlineStr">
+        <is>
+          <t>AG Occurrence</t>
+        </is>
+      </c>
+      <c r="H2" s="26" t="inlineStr">
+        <is>
+          <t>Dose per Administration</t>
+        </is>
+      </c>
+      <c r="I2" s="26" t="inlineStr">
+        <is>
+          <t>Dose Units</t>
+        </is>
+      </c>
+      <c r="J2" s="26" t="inlineStr">
+        <is>
+          <t>Treatment Vehicle
+Amount</t>
+        </is>
+      </c>
+      <c r="K2" s="26" t="inlineStr">
+        <is>
+          <t>Treatment Vehicle
+Amount Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="26" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="I3" s="26" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="26" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="26" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="26" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>XYZ-001-001</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Tuberculin PPD-S</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>tuberculin unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>XYZ-001-002</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Tuberculin PPD-S</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>tuberculin unit</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>